--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260703.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>894,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.25%</t>
+          <t>10.37%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>899,244,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.21%</t>
+          <t>10.34%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.71%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>184,786,000</t>
+          <t>185,192,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.14%</t>
         </is>
       </c>
     </row>
@@ -704,24 +704,24 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.24%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,999,000</t>
+          <t>112,174,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>4,999,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,88 +755,88 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,174,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>96,288,442</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>25,944,000</t>
+          <t>97,242,442</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>25,944,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,695</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>148,092,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
@@ -963,29 +963,29 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>131,297,000</t>
+          <t>131,997,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>146,892,000</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>226,166,516</t>
+          <t>1,615</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,167,000</t>
+          <t>99,767,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,44 +1063,44 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>62,290,000</t>
+          <t>371,675,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>367,675,000</t>
+          <t>62,290,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>274,866,000</t>
+          <t>277,366,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,443,000</t>
+          <t>14,523,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,144,193,710</t>
+          <t>7,736,080,464</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,997,981,743</t>
+          <t>7,131,336,703</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-516,639,761</t>
+          <t>-132,885,655</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
